--- a/data/trans_orig/Q5405-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Provincia-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66836</t>
+          <t>66878</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>73720</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86652</t>
+          <t>86360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>96103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146523</t>
+          <t>146637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159793</t>
+          <t>159733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78941</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128411</t>
+          <t>128043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54302</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66331</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73456</t>
+          <t>73459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>118583</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127522</t>
+          <t>127552</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111735</t>
+          <t>111924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98540</t>
+          <t>98761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>105116</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106578</t>
+          <t>105919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115322</t>
+          <t>115323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>208628</t>
+          <t>209159</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219507</t>
+          <t>219903</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>99021</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>109176</t>
+          <t>109233</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>128576</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>144710</t>
+          <t>145053</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>233011</t>
+          <t>232916</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>251227</t>
+          <t>251513</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>464648</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>484742</t>
+          <t>484327</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>650948</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1099327</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1128971</t>
+          <t>1130302</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>43347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47797</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>79720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89964</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55251</t>
+          <t>55742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72398</t>
+          <t>72641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76841</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>92401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160814</t>
+          <t>160794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52689</t>
+          <t>52711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>55572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70315</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>101785</t>
+          <t>101779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120708</t>
+          <t>119907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61947</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71174</t>
+          <t>71474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82330</t>
+          <t>82288</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127538</t>
+          <t>128345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142234</t>
+          <t>142169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>39253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47854</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65882</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>77428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57152</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66939</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95223</t>
+          <t>95208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>111138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97217</t>
+          <t>96297</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109054</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123119</t>
+          <t>123230</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>135812</t>
+          <t>135911</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>225125</t>
+          <t>225318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>242297</t>
+          <t>242455</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109885</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>119635</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>148811</t>
+          <t>148222</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>160208</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>261709</t>
+          <t>262926</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>277664</t>
+          <t>278280</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>67782</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>102167</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>486521</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>517838</t>
+          <t>517510</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>647417</t>
+          <t>648182</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>681466</t>
+          <t>681602</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1146378</t>
+          <t>1146537</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1192250</t>
+          <t>1191621</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44271</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62148</t>
+          <t>63273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>77281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102185</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113832</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188829</t>
+          <t>189269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201179</t>
+          <t>201168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>53083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61406</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>63486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76478</t>
+          <t>76166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119685</t>
+          <t>119888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135881</t>
+          <t>135803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82428</t>
+          <t>83830</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147104</t>
+          <t>147374</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>155453</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82267</t>
+          <t>81502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91456</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39043</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46683</t>
+          <t>46803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>53068</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64990</t>
+          <t>64944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97013</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110559</t>
+          <t>110044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101397</t>
+          <t>101933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110367</t>
+          <t>110417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123992</t>
+          <t>124669</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139725</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>230313</t>
+          <t>230170</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248613</t>
+          <t>248670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129170</t>
+          <t>129023</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>163175</t>
+          <t>163027</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>174951</t>
+          <t>174970</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>296393</t>
+          <t>296685</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>308256</t>
+          <t>308269</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>558402</t>
+          <t>557263</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>575653</t>
+          <t>575894</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>702817</t>
+          <t>702674</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>734475</t>
+          <t>735218</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1270269</t>
+          <t>1270290</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1305511</t>
+          <t>1305082</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -13974,27 +13974,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>59184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>54784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>62122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105733</t>
+          <t>113499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115078</t>
+          <t>122326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14239,22 +14239,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,17 +14274,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76269</t>
+          <t>83696</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71455</t>
+          <t>78252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79001</t>
+          <t>86541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>109771</t>
+          <t>114704</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>106764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115827</t>
+          <t>120566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>186040</t>
+          <t>198400</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178020</t>
+          <t>188545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192583</t>
+          <t>205689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,17 +14843,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>66755</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>62517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70592</t>
+          <t>69402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80554</t>
+          <t>79011</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75627</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>81900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148405</t>
+          <t>145765</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142775</t>
+          <t>140707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152379</t>
+          <t>150461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>722</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73453</t>
+          <t>81864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70565</t>
+          <t>78462</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98441</t>
+          <t>105103</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94906</t>
+          <t>101453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100867</t>
+          <t>107477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>171893</t>
+          <t>186967</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>168404</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174693</t>
+          <t>189729</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,32 +15642,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52537</t>
+          <t>54587</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48912</t>
+          <t>50763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>84819</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80531</t>
+          <t>83782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87818</t>
+          <t>91971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55836</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57919</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60355</t>
+          <t>61990</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>113332</t>
+          <t>114964</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>108970</t>
+          <t>110330</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116989</t>
+          <t>118411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16607,57 +16607,57 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>9380</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>12066</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -16710,27 +16710,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>121776</t>
+          <t>149710</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117957</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>332036</t>
+          <t>156211</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>317464</t>
+          <t>150062</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337793</t>
+          <t>160182</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>453811</t>
+          <t>305921</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>444133</t>
+          <t>298782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>460720</t>
+          <t>310128</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>181612</t>
+          <t>206590</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>176256</t>
+          <t>199198</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>183889</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>328692</t>
+          <t>370145</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>324003</t>
+          <t>362846</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>331333</t>
+          <t>373074</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>375417</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>375417</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>375417</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>39686</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53661</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>57709</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>628664</t>
+          <t>694410</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>620766</t>
+          <t>685616</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>635141</t>
+          <t>700632</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>969582</t>
+          <t>834530</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>949625</t>
+          <t>821131</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1002534</t>
+          <t>845724</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1598246</t>
+          <t>1528940</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1580236</t>
+          <t>1514621</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1625466</t>
+          <t>1542535</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
